--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/bio-bio.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/bio-bio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>53807.51</v>
+        <v>54058.1</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>31111.44</v>
+        <v>31272.12</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>49881.7</v>
+        <v>50233.74</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>60791.01</v>
+        <v>61220.05</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>114363.85</v>
+        <v>113953.77</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>75738.24000000001</v>
+        <v>75574.33</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>17522.1</v>
+        <v>17484.18</v>
       </c>
     </row>
     <row r="10">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>85921.94</v>
+        <v>86251.73</v>
       </c>
     </row>
     <row r="11">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>36638.34</v>
+        <v>37529.31</v>
       </c>
     </row>
     <row r="12">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>26461.43</v>
+        <v>27247.95</v>
       </c>
     </row>
     <row r="13">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>63090.62</v>
+        <v>63506.13</v>
       </c>
     </row>
     <row r="14">
@@ -1313,13 +1313,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>23529.45</v>
+        <v>23363.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2704-200-CM26</t>
+          <t>1456840-10-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.981.460-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1374,13 +1374,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>10759.72</v>
+        <v>24347.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1456840-10-CM26</t>
+          <t>2704-200-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.981.460-6</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1420,12 +1420,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>24520.46</v>
+        <v>10683.79</v>
       </c>
     </row>
     <row r="17">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>102600.5</v>
+        <v>104460.72</v>
       </c>
     </row>
     <row r="18">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>25295.04</v>
+        <v>24750.82</v>
       </c>
     </row>
     <row r="19">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>39677.35</v>
+        <v>39506.9</v>
       </c>
     </row>
     <row r="20">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>77937.53</v>
+        <v>79052.75</v>
       </c>
     </row>
     <row r="21">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>34997.99</v>
+        <v>34406.67</v>
       </c>
     </row>
     <row r="22">
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>54523.08</v>
+        <v>53773.91</v>
       </c>
     </row>
     <row r="23">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>107346.32</v>
+        <v>108064.84</v>
       </c>
     </row>
     <row r="24">
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>48560.21</v>
+        <v>48454.56</v>
       </c>
     </row>
     <row r="25">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>38267.34</v>
+        <v>37822.07</v>
       </c>
     </row>
     <row r="26">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>37580.16</v>
+        <v>37371.82</v>
       </c>
     </row>
     <row r="27">
@@ -2114,7 +2114,68 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>34372.75</v>
+        <v>34203.75</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2416-201-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.150.400-K</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>96.918.300-5</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>42840</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/bio-bio.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/bio-bio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4229-171-CM25</t>
+          <t>3607-16-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>69.170.500-5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>I MUNICIPALIDAD DE MULCHEN</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.918.300-5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>54058.1</v>
+        <v>70058.97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4020-1383-CM25</t>
+          <t>4359-202-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>31272.12</v>
+        <v>34461.19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>995118-180-CM25</t>
+          <t>4160-14-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>69.264.400-k</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>MUNICIPALIDAD DE HUALPEN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>50233.74</v>
+        <v>29659.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1347776-13-CM25</t>
+          <t>2078-265-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>61220.05</v>
+        <v>33656.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3319-249-CM25</t>
+          <t>4229-171-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>42056.86</v>
+        <v>54058.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>998-290-CM25</t>
+          <t>4020-1383-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,32 +859,28 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Janssen S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>81.198.100-1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de los Lagos </t>
-        </is>
-      </c>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>113953.77</v>
+        <v>31272.12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4414-1824-CM25</t>
+          <t>995118-180-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>VIII Zona de Carabineros Bio Bío</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -924,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -939,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>75574.33</v>
+        <v>50233.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1208129-774-CM25</t>
+          <t>1347776-13-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -975,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>96.918.300-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1000,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>17484.18</v>
+        <v>61220.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4237-77-CM25</t>
+          <t>3319-249-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.160.200-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1046,32 +1042,28 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tattersall Maquinarias S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>83.472.500-2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de los Lagos </t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>86251.73</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4829-12-CM26</t>
+          <t>998-290-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1081,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.264.600-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO BIOBIO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1111,28 +1103,32 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Janssen S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>81.198.100-1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>37529.31</v>
+        <v>113953.77</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>654-33-CM26</t>
+          <t>4414-1824-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1142,27 +1138,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1172,12 +1168,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1187,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>27247.95</v>
+        <v>75574.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2410-5-CM26</t>
+          <t>1208129-774-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1203,12 +1199,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1218,12 +1214,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1233,32 +1229,28 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>63506.13</v>
+        <v>17484.18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3945-128-CM26</t>
+          <t>4237-77-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1268,27 +1260,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.160.400-4</t>
+          <t>69.160.200-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1298,28 +1290,32 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Tattersall Maquinarias S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>83.472.500-2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>23363.4</v>
+        <v>86251.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1456840-10-CM26</t>
+          <t>4829-12-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1329,27 +1325,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.981.460-6</t>
+          <t>69.264.600-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO BIOBIO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1359,12 +1355,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1374,13 +1370,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>24347.42</v>
+        <v>37529.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2704-200-CM26</t>
+          <t>654-33-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1390,12 +1386,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1405,12 +1401,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1420,12 +1416,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1435,13 +1431,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10683.79</v>
+        <v>27247.95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4988-6-CM26</t>
+          <t>2410-5-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1451,27 +1447,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1481,17 +1477,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Guillermo Morales Ltda</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.564.810-0</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Región ;Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1500,13 +1496,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>104460.72</v>
+        <v>63506.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4362-22-CM26</t>
+          <t>2704-200-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1521,22 +1517,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1546,12 +1542,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1561,28 +1557,28 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>24750.82</v>
+        <v>10683.79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1208910-77-CM26</t>
+          <t>1456840-10-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1592,12 +1588,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>65.201.852-1</t>
+          <t>61.981.460-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1607,12 +1603,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1622,43 +1618,43 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>39506.9</v>
+        <v>24347.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1079650-31-CM26</t>
+          <t>3945-128-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>69.160.400-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1668,12 +1664,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1683,28 +1679,28 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>79052.75</v>
+        <v>23363.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3977-52-CM26</t>
+          <t>4988-6-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1714,12 +1710,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.170.202-2</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Santa Barbara - Salud</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1729,43 +1725,47 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>Guillermo Morales Ltda</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>96.564.810-0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Región ;Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>34406.67</v>
+        <v>104460.72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4414-752-CM26</t>
+          <t>4362-22-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1805,13 +1805,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>53773.91</v>
+        <v>24750.82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4034-309-CM26</t>
+          <t>1208910-77-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1821,27 +1821,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>65.201.852-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1851,32 +1851,28 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
-        </is>
-      </c>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>108064.84</v>
+        <v>39506.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3801-36-CM26</t>
+          <t>1079650-31-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1886,12 +1882,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1901,12 +1897,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.172.600-2</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILACO</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1916,12 +1912,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AUTO SUMMIT CHILE S.A.</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.924.460-8</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1931,13 +1927,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>48454.56</v>
+        <v>79052.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4236-511-CM26</t>
+          <t>3977-52-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1947,12 +1943,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1962,12 +1958,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.160.200-1</t>
+          <t>69.170.202-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>Ilustre Municipalidad de Santa Barbara - Salud</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1977,12 +1973,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1992,13 +1988,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>37822.07</v>
+        <v>34406.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4083-352-CM26</t>
+          <t>4414-752-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2008,12 +2004,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2023,12 +2019,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2038,12 +2034,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2053,13 +2049,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>37371.82</v>
+        <v>53773.91</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4494-544-CM26</t>
+          <t>4034-309-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2074,7 +2070,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2084,12 +2080,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>Ilustre Municipalidad de Cañete - Educación</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2099,28 +2095,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>96.918.300-5</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>34203.75</v>
+        <v>108064.84</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2416-201-CM26</t>
+          <t>3801-36-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.172.600-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE QUILACO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>AUTO SUMMIT CHILE S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>96.924.460-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2175,6 +2175,250 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
+        <v>48454.56</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4236-511-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.160.200-1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>37822.07</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4083-352-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.151.002-6</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>37371.82</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4494-544-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>69.150.500-6</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PENCO</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>34203.75</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2416-201-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>69.150.400-K</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>96.918.300-5</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
         <v>42840</v>
       </c>
     </row>
